--- a/data/proc_data/public_data/2025_idc_design.xlsx
+++ b/data/proc_data/public_data/2025_idc_design.xlsx
@@ -35608,7 +35608,7 @@
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>Medio bajo</t>
+          <t>Medio Bajo</t>
         </is>
       </c>
       <c r="X311">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>Medio bajo</t>
+          <t>Medio Bajo</t>
         </is>
       </c>
       <c r="X329">

--- a/data/proc_data/public_data/2025_idc_design.xlsx
+++ b/data/proc_data/public_data/2025_idc_design.xlsx
@@ -35608,7 +35608,7 @@
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>Medio Bajo</t>
+          <t>Medio bajo</t>
         </is>
       </c>
       <c r="X311">
@@ -37630,7 +37630,7 @@
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>Medio Bajo</t>
+          <t>Medio bajo</t>
         </is>
       </c>
       <c r="X329">
